--- a/samples/sample_input.xlsx
+++ b/samples/sample_input.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>A 15% discount for lack of marketability is applied to the subsidiary's equity value because the shares are unlisted and a minority buyer would face a long sale process. Liquidation values apply recovery percentages that reflect a forced sale within the liquidation timeline.</t>
+          <t>A 15% discount for lack of marketability is applied to the subsidiary's equity value because the shares are unlisted and a buyer would face a long sale process. Liquidation values apply recovery percentages that reflect a forced sale within the liquidation timeline.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
